--- a/Datos_Agua.xlsx
+++ b/Datos_Agua.xlsx
@@ -461,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
@@ -541,11 +541,6 @@
       </c>
       <c r="E4" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
